--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -321,7 +321,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -573,7 +573,7 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
@@ -1409,7 +1409,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1471,7 +1471,7 @@
     <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -1494,7 +1494,7 @@
     <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
